--- a/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
+++ b/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UserPC\Desktop\Local Disk D\Stevan - Tenderi\WEB\PROG\Portfolio\tehnohaus.mk\katalozi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UserPC\Desktop\Local Disk D\Stevan - Tenderi\WEB\PROG\Portfolio\Javascript Vanilla\tehnohaus.mk\katalozi\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="CetaForm" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Altec" sheetId="10" r:id="rId11"/>
     <sheet name="Stubai" sheetId="11" r:id="rId12"/>
     <sheet name="HFS" sheetId="12" r:id="rId13"/>
+    <sheet name="Insize (2)" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="473">
   <si>
     <t>TOOL CONTAINERS AND ASSORTMENTS</t>
   </si>
@@ -200,9 +201,6 @@
     <t>Битови и додатоци</t>
   </si>
   <si>
-    <t>Насадни клучеви и сетови</t>
-  </si>
-  <si>
     <t>.3-7</t>
   </si>
   <si>
@@ -237,9 +235,6 @@
   </si>
   <si>
     <t>Менгемиња</t>
-  </si>
-  <si>
-    <t>Водовод</t>
   </si>
   <si>
     <t>Торби, држачи и кутии за алат</t>
@@ -963,9 +958,6 @@
     <t>AluLight S-Двојна ограда</t>
   </si>
   <si>
-    <t>AluLight Удобна кула за скали</t>
-  </si>
-  <si>
     <t>Делови за AluLight</t>
   </si>
   <si>
@@ -975,9 +967,6 @@
     <t>Мултистеги</t>
   </si>
   <si>
-    <t>Лесни поддршки</t>
-  </si>
-  <si>
     <t>Мали стеги</t>
   </si>
   <si>
@@ -996,21 +985,9 @@
     <t>Еднорачни стеги</t>
   </si>
   <si>
-    <t>LE VER стеги</t>
-  </si>
-  <si>
-    <t>За дупки и водичи</t>
-  </si>
-  <si>
     <t>Пружински стеги</t>
   </si>
   <si>
-    <t>Прогресивни рачни стеги за притисок</t>
-  </si>
-  <si>
-    <t>Професионални челични лентачни стеги</t>
-  </si>
-  <si>
     <t>Стеги со ремен</t>
   </si>
   <si>
@@ -1023,66 +1000,18 @@
     <t>Менгеме стеги</t>
   </si>
   <si>
-    <t>За работа на метални и дрвени маси со дупки</t>
-  </si>
-  <si>
-    <t>За дрвена маса</t>
-  </si>
-  <si>
-    <t>TGA · Брза самоприлагодлива стега со копче</t>
-  </si>
-  <si>
     <t>TS · Универзални завртки и стопирачки</t>
   </si>
   <si>
-    <t>TCS · Стеги и позиционатори за маси со дупки</t>
-  </si>
-  <si>
-    <t>Превртувачки стеги</t>
-  </si>
-  <si>
-    <t>Клешти за заклучување</t>
-  </si>
-  <si>
-    <t>Магнетни алати за заварување</t>
-  </si>
-  <si>
-    <t>Чаши за вшмукување</t>
-  </si>
-  <si>
     <t>Подигнувачи и транспортери</t>
   </si>
   <si>
-    <t>"Коњи" за транспортирање и пилирање</t>
-  </si>
-  <si>
     <t>Изложбени полици</t>
   </si>
   <si>
-    <t>Ударни клучеви</t>
-  </si>
-  <si>
-    <t>Моментни клучеви и наноси</t>
-  </si>
-  <si>
-    <t>Рецчелки</t>
-  </si>
-  <si>
-    <t>Чекани со длето и иглички</t>
-  </si>
-  <si>
-    <t>Брусилки</t>
-  </si>
-  <si>
     <t>Мулти-брусалка MBX</t>
   </si>
   <si>
-    <t>Полирачи</t>
-  </si>
-  <si>
-    <t>Заковувачи</t>
-  </si>
-  <si>
     <t>Дигалки за автомобили</t>
   </si>
   <si>
@@ -1101,21 +1030,12 @@
     <t>Мини алати</t>
   </si>
   <si>
-    <t>Специјални алати и сечење</t>
-  </si>
-  <si>
     <t>Други пневматски алати</t>
   </si>
   <si>
-    <t>Стартер на кондензатор</t>
-  </si>
-  <si>
     <t>Додатоци за воздушни линии</t>
   </si>
   <si>
-    <t>Клучеви за врезници</t>
-  </si>
-  <si>
     <t>Рачни врезници</t>
   </si>
   <si>
@@ -1146,9 +1066,6 @@
     <t>Индустриски кабинети</t>
   </si>
   <si>
-    <t>LinBin системи</t>
-  </si>
-  <si>
     <t>Работни маси</t>
   </si>
   <si>
@@ -1158,18 +1075,9 @@
     <t>Колички за ракување и алати</t>
   </si>
   <si>
-    <t>Штипки</t>
-  </si>
-  <si>
-    <t>Системи за полици</t>
-  </si>
-  <si>
     <t>Додатоци и етикетирање</t>
   </si>
   <si>
-    <t>Кабинети со иоки</t>
-  </si>
-  <si>
     <t>Кабинети за CNC алати</t>
   </si>
   <si>
@@ -1179,63 +1087,18 @@
     <t>Кабинети за материјали</t>
   </si>
   <si>
-    <t>PPE шкафови</t>
-  </si>
-  <si>
-    <t>Дијамантски сечила за пила</t>
-  </si>
-  <si>
-    <t>Алатки за дијамантско брусење</t>
-  </si>
-  <si>
-    <t>Прстени за дијамантско сечење</t>
-  </si>
-  <si>
-    <t>Обработка на плочки</t>
-  </si>
-  <si>
-    <t>Опрема за дупчење со јадро</t>
-  </si>
-  <si>
     <t>Додатоци</t>
   </si>
   <si>
     <t>Машини за сечење</t>
   </si>
   <si>
-    <t>Бушалки со суво јадро</t>
-  </si>
-  <si>
-    <t>Бушалки и шрафцигери</t>
-  </si>
-  <si>
-    <t>Бушалки со влажно јадро</t>
-  </si>
-  <si>
-    <t>Чекан-дупчалки</t>
-  </si>
-  <si>
     <t>Длета</t>
   </si>
   <si>
-    <t>Дупчалки за метал</t>
-  </si>
-  <si>
-    <t>Дупчалки за дрво</t>
-  </si>
-  <si>
     <t>Пили</t>
   </si>
   <si>
-    <t>Асортиман</t>
-  </si>
-  <si>
-    <t>Модули</t>
-  </si>
-  <si>
-    <t>Специјални и дупчалки за камен</t>
-  </si>
-  <si>
     <t>Кутии и колички за алат</t>
   </si>
   <si>
@@ -1276,6 +1139,324 @@
   </si>
   <si>
     <t>Алати за одржување</t>
+  </si>
+  <si>
+    <t>Насадни клучеви, сетови и прибор</t>
+  </si>
+  <si>
+    <t>Алат за водовод</t>
+  </si>
+  <si>
+    <t>Бургии за електропневматски чекан</t>
+  </si>
+  <si>
+    <t>Бургии за вибрациона дупчалка</t>
+  </si>
+  <si>
+    <t>Бургии за метал</t>
+  </si>
+  <si>
+    <t>Бургии за дрво</t>
+  </si>
+  <si>
+    <t>Комплети</t>
+  </si>
+  <si>
+    <t>Продажни модули</t>
+  </si>
+  <si>
+    <t>Дијамантски пили</t>
+  </si>
+  <si>
+    <t>Дијамантски круни за бушење</t>
+  </si>
+  <si>
+    <t>Дијамантски алат за брусење</t>
+  </si>
+  <si>
+    <t>Дијамантски круни за суво бушење</t>
+  </si>
+  <si>
+    <t>Дијамантски круни за водено бушење</t>
+  </si>
+  <si>
+    <t>Круни и алат за обработка на плочки</t>
+  </si>
+  <si>
+    <t>Дупчалки за бушење со круни</t>
+  </si>
+  <si>
+    <t>Кабинети со фиоки</t>
+  </si>
+  <si>
+    <t>Ормари за лична заштитна опрема</t>
+  </si>
+  <si>
+    <t>LinBin системи за складирање</t>
+  </si>
+  <si>
+    <t>Прибор за работни маси</t>
+  </si>
+  <si>
+    <t>Сталажи</t>
+  </si>
+  <si>
+    <t>Држачи за врезници и нарезници</t>
+  </si>
+  <si>
+    <t>Пневматски одвртувачи</t>
+  </si>
+  <si>
+    <t>Моментни клучеви и прибор</t>
+  </si>
+  <si>
+    <t>Крцкалки</t>
+  </si>
+  <si>
+    <t>Пневматски дупчалки и одвртувачи</t>
+  </si>
+  <si>
+    <t>Пневматски чекани и прибор</t>
+  </si>
+  <si>
+    <t>Пневматски брусалки</t>
+  </si>
+  <si>
+    <t>Пневматски полирки</t>
+  </si>
+  <si>
+    <t>Пневматски алати за сечење</t>
+  </si>
+  <si>
+    <t>Пневматски поп-клешти</t>
+  </si>
+  <si>
+    <t>Стартери</t>
+  </si>
+  <si>
+    <t>Телескопски потпирачи</t>
+  </si>
+  <si>
+    <t>Стеги - MAXIPRESS</t>
+  </si>
+  <si>
+    <t>Стеги со лостови - LE VER</t>
+  </si>
+  <si>
+    <t>Стеги за дупки и водилки</t>
+  </si>
+  <si>
+    <t>Рачни стеги за притисок</t>
+  </si>
+  <si>
+    <t>Челични стеги за рамки</t>
+  </si>
+  <si>
+    <t>Стеги за работа на метални и дрвени маси со дупки</t>
+  </si>
+  <si>
+    <t>Стеги за дрвена маса</t>
+  </si>
+  <si>
+    <t>TCS · Стеги и позиционери за маси со дупки</t>
+  </si>
+  <si>
+    <t>Брзи стеги</t>
+  </si>
+  <si>
+    <t>TGA · Грип-стеги</t>
+  </si>
+  <si>
+    <t>Грип клешти</t>
+  </si>
+  <si>
+    <t>Магнетни прибор за заварување</t>
+  </si>
+  <si>
+    <t>Вакум рачки</t>
+  </si>
+  <si>
+    <t>Платформа за пилирање</t>
+  </si>
+  <si>
+    <t>AluLight Професионално подвижно скеле со скали</t>
+  </si>
+  <si>
+    <t>AluSteg - мостови за скелиња</t>
+  </si>
+  <si>
+    <t>АЛАТ ЗА ПОПРАВКА НА НАВОЈ</t>
+  </si>
+  <si>
+    <t>Експорт на податоци и софтвер</t>
+  </si>
+  <si>
+    <t>Шублери</t>
+  </si>
+  <si>
+    <t>Мерачи на длабочина</t>
+  </si>
+  <si>
+    <t>Мерачи на висина</t>
+  </si>
+  <si>
+    <t>Компаратори</t>
+  </si>
+  <si>
+    <t>Микрометри</t>
+  </si>
+  <si>
+    <t>Мерачи на дијаметар и опсег на отвори</t>
+  </si>
+  <si>
+    <t>Мерачи на радиус на лак</t>
+  </si>
+  <si>
+    <t>Мерачи на жлебови за клучеви</t>
+  </si>
+  <si>
+    <t>Мерачи на косини</t>
+  </si>
+  <si>
+    <t>Индикатори, линеарни мерила, држачи за индикатори</t>
+  </si>
+  <si>
+    <t>Различни мерни инструменти со индикатор</t>
+  </si>
+  <si>
+    <t>Мерачи на навои на цевки</t>
+  </si>
+  <si>
+    <t>Стандарди и мерни блокови</t>
+  </si>
+  <si>
+    <t>Мерачи на агол, правост, рамнина</t>
+  </si>
+  <si>
+    <t>Тестери за концентричност и биење</t>
+  </si>
+  <si>
+    <t>Едноставни мерни алати</t>
+  </si>
+  <si>
+    <t>Прибор за поставување</t>
+  </si>
+  <si>
+    <t>Машински мерачи</t>
+  </si>
+  <si>
+    <t>Рачни и машински либели</t>
+  </si>
+  <si>
+    <t>Линеари, дигитални индикатори, воздушни мерила, тестери за истекување на воздух, ласерски скен микрометри, спектрометри, преднаместувачи на алати</t>
+  </si>
+  <si>
+    <t>Разновидни детектори</t>
+  </si>
+  <si>
+    <t>(cmm) координатни мерни машини</t>
+  </si>
+  <si>
+    <t>Профил проектори, системи за брзо мерење, визуелни мерни системи</t>
+  </si>
+  <si>
+    <t>Микроскопи, лупи</t>
+  </si>
+  <si>
+    <t>Видеоскопи</t>
+  </si>
+  <si>
+    <t>Мерачи на наслаги</t>
+  </si>
+  <si>
+    <t>Преносливи инструменти</t>
+  </si>
+  <si>
+    <t>Електронско тестирање</t>
+  </si>
+  <si>
+    <t>Мерачи на температура и влажност</t>
+  </si>
+  <si>
+    <t>Мерачи за кружност, профил и рапавост</t>
+  </si>
+  <si>
+    <t>Мерачи за тврдина</t>
+  </si>
+  <si>
+    <t>Подготовка за металографија</t>
+  </si>
+  <si>
+    <t>Мерачи на силина</t>
+  </si>
+  <si>
+    <t>Мерачи на вртежен момент, клучеви за вртежен момент</t>
+  </si>
+  <si>
+    <t>Ваги</t>
+  </si>
+  <si>
+    <t>Мерач на спреј на сол, комори за температура и влажност</t>
+  </si>
+  <si>
+    <t>Insize 1. Експорт на податоци и софтвер</t>
+  </si>
+  <si>
+    <t>Insize 10. Мерачи на косини</t>
+  </si>
+  <si>
+    <t>Insize 2. Шублери</t>
+  </si>
+  <si>
+    <t>Insize 3. Мерачи на длабочина</t>
+  </si>
+  <si>
+    <t>Insize 4. Мерачи на висина</t>
+  </si>
+  <si>
+    <t>Insize 5. Компаратори</t>
+  </si>
+  <si>
+    <t>Insize 6. Микрометри</t>
+  </si>
+  <si>
+    <t>Insize 7. Мерачи на дијаметар и опсег на отвори</t>
+  </si>
+  <si>
+    <t>Insize 8. Мерачи на радиус на лак</t>
+  </si>
+  <si>
+    <t>Insize 9. Мерачи на жлебови за клучеви</t>
+  </si>
+  <si>
+    <t>Insize 1. DATA OUTPUT AND SOFTWARE.pdf</t>
+  </si>
+  <si>
+    <t>Insize 2. CALIPERS.pdf</t>
+  </si>
+  <si>
+    <t>Insize 3. DEPTH MEASUREMENT.pdf</t>
+  </si>
+  <si>
+    <t>Insize 4. HEIGHT MEASUREMENT.pdf</t>
+  </si>
+  <si>
+    <t>Insize 5. COMPARISON INSTRUMENTS.pdf</t>
+  </si>
+  <si>
+    <t>Insize 6. MICROMETERS.pdf</t>
+  </si>
+  <si>
+    <t>Insize 7. BORE DIAMETER, CIRCUMFERENCE MEASUREMENT.pdf</t>
+  </si>
+  <si>
+    <t>Insize 8. ARC RADIUS MEASUREMENT.pdf</t>
+  </si>
+  <si>
+    <t>Insize 9. KEYWAY MEASUREMENT.pdf</t>
+  </si>
+  <si>
+    <t>Insize 10. CHAMFER MEASUREMENT.pdf</t>
   </si>
 </sst>
 </file>
@@ -1300,12 +1481,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1320,11 +1507,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1892,8 +2080,8 @@
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="G3" t="s">
-        <v>399</v>
+      <c r="G3" s="4" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1903,8 +2091,8 @@
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" t="s">
-        <v>400</v>
+      <c r="G4" s="4" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1914,8 +2102,8 @@
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
-        <v>401</v>
+      <c r="G5" s="4" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1925,8 +2113,8 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="G6" t="s">
-        <v>402</v>
+      <c r="G6" s="4" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1936,8 +2124,8 @@
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="G7" t="s">
-        <v>403</v>
+      <c r="G7" s="4" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1947,8 +2135,8 @@
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" t="s">
-        <v>404</v>
+      <c r="G8" s="4" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1958,8 +2146,8 @@
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="G9" t="s">
-        <v>405</v>
+      <c r="G9" s="4" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1969,8 +2157,8 @@
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="G10" t="s">
-        <v>406</v>
+      <c r="G10" s="4" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1980,8 +2168,8 @@
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="G11" t="s">
-        <v>407</v>
+      <c r="G11" s="4" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1991,8 +2179,8 @@
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="G12" t="s">
-        <v>408</v>
+      <c r="G12" s="4" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2002,8 +2190,8 @@
       <c r="B13" t="s">
         <v>20</v>
       </c>
-      <c r="G13" t="s">
-        <v>409</v>
+      <c r="G13" s="4" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2013,8 +2201,8 @@
       <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="G14" t="s">
-        <v>410</v>
+      <c r="G14" s="4" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2024,8 +2212,8 @@
       <c r="B15" t="s">
         <v>24</v>
       </c>
-      <c r="G15" t="s">
-        <v>411</v>
+      <c r="G15" s="4" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2035,8 +2223,8 @@
       <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="G16" t="s">
-        <v>412</v>
+      <c r="G16" s="4" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -2055,7 +2243,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2063,13 +2251,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J3" t="s">
-        <v>312</v>
+        <v>200</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2077,13 +2265,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
-      </c>
-      <c r="J4" t="s">
-        <v>311</v>
+        <v>202</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2091,13 +2279,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
-      </c>
-      <c r="J5" t="s">
-        <v>205</v>
+        <v>203</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2105,13 +2293,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D6" t="s">
-        <v>207</v>
-      </c>
-      <c r="J6" t="s">
-        <v>313</v>
+        <v>205</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2119,13 +2307,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
-      </c>
-      <c r="J7" t="s">
-        <v>314</v>
+        <v>207</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2133,13 +2321,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D8" t="s">
-        <v>210</v>
-      </c>
-      <c r="J8" t="s">
-        <v>315</v>
+        <v>208</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2147,13 +2335,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D9" t="s">
-        <v>212</v>
-      </c>
-      <c r="J9" t="s">
-        <v>316</v>
+        <v>210</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2161,13 +2349,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D10" t="s">
-        <v>214</v>
-      </c>
-      <c r="J10" t="s">
-        <v>317</v>
+        <v>212</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2175,13 +2363,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D11" t="s">
-        <v>216</v>
-      </c>
-      <c r="J11" t="s">
-        <v>318</v>
+        <v>214</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -2189,13 +2377,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
-      </c>
-      <c r="J12" t="s">
-        <v>319</v>
+        <v>216</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -2203,13 +2391,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
-      </c>
-      <c r="J13" t="s">
-        <v>320</v>
+        <v>218</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2217,13 +2405,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D14" t="s">
-        <v>222</v>
-      </c>
-      <c r="J14" t="s">
-        <v>321</v>
+        <v>220</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2231,13 +2419,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D15" t="s">
-        <v>224</v>
-      </c>
-      <c r="J15" t="s">
-        <v>322</v>
+        <v>222</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -2245,13 +2433,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D16" t="s">
-        <v>226</v>
-      </c>
-      <c r="J16" t="s">
-        <v>323</v>
+        <v>224</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -2259,13 +2447,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D17" t="s">
-        <v>228</v>
-      </c>
-      <c r="J17" t="s">
-        <v>324</v>
+        <v>226</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
@@ -2273,13 +2461,13 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
-        <v>230</v>
-      </c>
-      <c r="J18" t="s">
-        <v>325</v>
+        <v>228</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
@@ -2287,13 +2475,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
-      </c>
-      <c r="J19" t="s">
-        <v>326</v>
+        <v>230</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
@@ -2301,13 +2489,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D20" t="s">
-        <v>234</v>
-      </c>
-      <c r="J20" t="s">
-        <v>327</v>
+        <v>232</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
@@ -2315,13 +2503,13 @@
         <v>19</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D21" t="s">
-        <v>236</v>
-      </c>
-      <c r="J21" t="s">
-        <v>328</v>
+        <v>234</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
@@ -2329,13 +2517,13 @@
         <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D22" t="s">
-        <v>239</v>
-      </c>
-      <c r="J22" t="s">
-        <v>329</v>
+        <v>237</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
@@ -2343,13 +2531,13 @@
         <v>21</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D23" t="s">
-        <v>241</v>
-      </c>
-      <c r="J23" t="s">
-        <v>330</v>
+        <v>239</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
@@ -2357,13 +2545,13 @@
         <v>22</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D24" t="s">
-        <v>243</v>
-      </c>
-      <c r="J24" t="s">
-        <v>331</v>
+        <v>241</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
@@ -2371,13 +2559,13 @@
         <v>23</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D25" t="s">
-        <v>245</v>
-      </c>
-      <c r="J25" t="s">
-        <v>332</v>
+        <v>243</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
@@ -2385,13 +2573,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D26" t="s">
-        <v>247</v>
-      </c>
-      <c r="J26" t="s">
-        <v>333</v>
+        <v>245</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
@@ -2399,13 +2587,13 @@
         <v>25</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D27" t="s">
-        <v>249</v>
-      </c>
-      <c r="J27" t="s">
-        <v>334</v>
+        <v>247</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
@@ -2413,13 +2601,13 @@
         <v>26</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D28" t="s">
-        <v>251</v>
-      </c>
-      <c r="J28" t="s">
-        <v>335</v>
+        <v>249</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
@@ -2427,13 +2615,13 @@
         <v>27</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D29" t="s">
-        <v>253</v>
-      </c>
-      <c r="J29" t="s">
-        <v>336</v>
+        <v>251</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
@@ -2441,13 +2629,13 @@
         <v>28</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D30" t="s">
-        <v>255</v>
-      </c>
-      <c r="J30" t="s">
-        <v>337</v>
+        <v>253</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
@@ -2455,13 +2643,13 @@
         <v>29</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D31" t="s">
-        <v>257</v>
-      </c>
-      <c r="J31" t="s">
-        <v>338</v>
+        <v>255</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
@@ -2469,13 +2657,13 @@
         <v>30</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D32" t="s">
-        <v>260</v>
-      </c>
-      <c r="J32" t="s">
-        <v>339</v>
+        <v>258</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -2493,245 +2681,245 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J2" t="s">
-        <v>296</v>
+        <v>260</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
-      </c>
-      <c r="J3" t="s">
-        <v>297</v>
+        <v>261</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>264</v>
-      </c>
-      <c r="J4" t="s">
-        <v>298</v>
+        <v>262</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>286</v>
-      </c>
-      <c r="J5" t="s">
-        <v>299</v>
+        <v>284</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>287</v>
-      </c>
-      <c r="J6" t="s">
-        <v>300</v>
+        <v>285</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>265</v>
-      </c>
-      <c r="J7" t="s">
-        <v>301</v>
+        <v>263</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>288</v>
-      </c>
-      <c r="J8" t="s">
-        <v>302</v>
+        <v>286</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
-      </c>
-      <c r="J9" t="s">
-        <v>303</v>
+        <v>287</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>290</v>
-      </c>
-      <c r="J10" t="s">
-        <v>290</v>
+        <v>288</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>291</v>
-      </c>
-      <c r="J11" t="s">
-        <v>310</v>
+        <v>289</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>266</v>
-      </c>
-      <c r="J12" t="s">
-        <v>304</v>
+        <v>264</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C13">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>292</v>
-      </c>
-      <c r="J13" t="s">
-        <v>305</v>
+        <v>290</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C14">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>293</v>
-      </c>
-      <c r="J14" t="s">
-        <v>306</v>
+        <v>291</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C15">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>294</v>
-      </c>
-      <c r="J15" t="s">
-        <v>307</v>
+        <v>292</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>295</v>
-      </c>
-      <c r="J16" t="s">
-        <v>308</v>
+        <v>293</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C17">
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>267</v>
-      </c>
-      <c r="J17" t="s">
-        <v>309</v>
+        <v>265</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C18">
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>268</v>
-      </c>
-      <c r="J18" t="s">
-        <v>268</v>
+        <v>266</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -2757,6 +2945,137 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:C11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C2" t="str">
+        <f>"Rename-Item -LiteralPath '"&amp;A2&amp;"' -NewName """&amp;SUBSTITUTE(B2,"""","`"") &amp; """"")</f>
+        <v>Rename-Item -LiteralPath 'Insize 1. DATA OUTPUT AND SOFTWARE.pdf' -NewName "Insize 1. Експорт на податоци и софтвер</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" ref="C3:C11" si="0">"Rename-Item -LiteralPath '"&amp;A3&amp;"' -NewName """&amp;SUBSTITUTE(B3,"""","`"") &amp; """"")</f>
+        <v>Rename-Item -LiteralPath 'Insize 2. CALIPERS.pdf' -NewName "Insize 2. Шублери</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>Rename-Item -LiteralPath 'Insize 3. DEPTH MEASUREMENT.pdf' -NewName "Insize 3. Мерачи на длабочина</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>Rename-Item -LiteralPath 'Insize 4. HEIGHT MEASUREMENT.pdf' -NewName "Insize 4. Мерачи на висина</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>Rename-Item -LiteralPath 'Insize 5. COMPARISON INSTRUMENTS.pdf' -NewName "Insize 5. Компаратори</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>468</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>Rename-Item -LiteralPath 'Insize 6. MICROMETERS.pdf' -NewName "Insize 6. Микрометри</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>469</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>Rename-Item -LiteralPath 'Insize 7. BORE DIAMETER, CIRCUMFERENCE MEASUREMENT.pdf' -NewName "Insize 7. Мерачи на дијаметар и опсег на отвори</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>Rename-Item -LiteralPath 'Insize 8. ARC RADIUS MEASUREMENT.pdf' -NewName "Insize 8. Мерачи на радиус на лак</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>471</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>Rename-Item -LiteralPath 'Insize 9. KEYWAY MEASUREMENT.pdf' -NewName "Insize 9. Мерачи на жлебови за клучеви</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>472</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>Rename-Item -LiteralPath 'Insize 10. CHAMFER MEASUREMENT.pdf' -NewName "Insize 10. Мерачи на косини</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q21"/>
@@ -2781,9 +3100,9 @@
         <v>1</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>50</v>
       </c>
       <c r="Q4" t="s">
@@ -2798,10 +3117,10 @@
         <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N5" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>367</v>
       </c>
       <c r="Q5" t="s">
         <v>30</v>
@@ -2817,7 +3136,7 @@
       <c r="M6">
         <v>15</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="4" t="s">
         <v>51</v>
       </c>
       <c r="Q6" t="s">
@@ -2832,13 +3151,13 @@
         <v>4</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" t="s">
-        <v>65</v>
+        <v>56</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="Q7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -2849,9 +3168,9 @@
         <v>5</v>
       </c>
       <c r="M8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="4" t="s">
         <v>52</v>
       </c>
       <c r="Q8" t="s">
@@ -2866,10 +3185,10 @@
         <v>6</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" t="s">
         <v>61</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="Q9" t="s">
         <v>35</v>
@@ -2885,11 +3204,11 @@
       <c r="M10">
         <v>28</v>
       </c>
-      <c r="N10" t="s">
-        <v>59</v>
+      <c r="N10" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="Q10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -2900,13 +3219,13 @@
         <v>8</v>
       </c>
       <c r="M11" t="s">
-        <v>60</v>
-      </c>
-      <c r="N11" t="s">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="Q11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -2919,11 +3238,11 @@
       <c r="M12">
         <v>31</v>
       </c>
-      <c r="N12" t="s">
-        <v>64</v>
+      <c r="N12" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="Q12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -2936,8 +3255,8 @@
       <c r="M13">
         <v>32</v>
       </c>
-      <c r="N13" t="s">
-        <v>66</v>
+      <c r="N13" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="Q13" t="s">
         <v>43</v>
@@ -2953,8 +3272,8 @@
       <c r="M14">
         <v>33</v>
       </c>
-      <c r="N14" t="s">
-        <v>67</v>
+      <c r="N14" s="4" t="s">
+        <v>368</v>
       </c>
       <c r="Q14" t="s">
         <v>44</v>
@@ -2970,11 +3289,11 @@
       <c r="M15">
         <v>34</v>
       </c>
-      <c r="N15" t="s">
-        <v>200</v>
+      <c r="N15" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="Q15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -2985,13 +3304,13 @@
         <v>13</v>
       </c>
       <c r="M16" t="s">
-        <v>69</v>
-      </c>
-      <c r="N16" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="Q16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
@@ -3002,9 +3321,9 @@
         <v>14</v>
       </c>
       <c r="M17" t="s">
-        <v>70</v>
-      </c>
-      <c r="N17" t="s">
+        <v>68</v>
+      </c>
+      <c r="N17" s="4" t="s">
         <v>53</v>
       </c>
       <c r="Q17" t="s">
@@ -3044,14 +3363,14 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3059,15 +3378,15 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="G4" t="s">
-        <v>171</v>
+      <c r="G4" s="4" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3075,31 +3394,31 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="G6" t="s">
-        <v>172</v>
+      <c r="G6" s="4" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="G7" t="s">
-        <v>173</v>
+      <c r="G7" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="G8" t="s">
-        <v>174</v>
+      <c r="G8" s="4" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3107,80 +3426,80 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="G10" t="s">
-        <v>175</v>
+      <c r="G10" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="G11" t="s">
-        <v>176</v>
+      <c r="G11" s="4" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="G12" t="s">
-        <v>177</v>
+      <c r="G12" s="4" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="G13" t="s">
-        <v>178</v>
+      <c r="G13" s="4" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="G14" t="s">
-        <v>179</v>
+      <c r="G14" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="G15" t="s">
-        <v>180</v>
+      <c r="G15" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="G16" t="s">
-        <v>181</v>
+      <c r="G16" s="4" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="G17" t="s">
-        <v>182</v>
+      <c r="G17" s="4" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="G18" t="s">
-        <v>183</v>
+      <c r="G18" s="4" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="G19" t="s">
-        <v>184</v>
+      <c r="G19" s="4" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -3191,308 +3510,419 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>106</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -3508,12 +3938,12 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -3521,13 +3951,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
-        <v>391</v>
+      <c r="G3" s="4" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3535,13 +3965,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
-        <v>392</v>
+      <c r="G4" s="4" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3549,13 +3979,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>23</v>
       </c>
-      <c r="G5" t="s">
-        <v>398</v>
+      <c r="G5" s="4" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3563,13 +3993,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E6">
         <v>37</v>
       </c>
-      <c r="G6" t="s">
-        <v>393</v>
+      <c r="G6" s="4" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3577,13 +4007,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7">
         <v>59</v>
       </c>
-      <c r="G7" t="s">
-        <v>394</v>
+      <c r="G7" s="4" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3591,13 +4021,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E8">
         <v>66</v>
       </c>
-      <c r="G8" t="s">
-        <v>395</v>
+      <c r="G8" s="4" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3605,13 +4035,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E9">
         <v>69</v>
       </c>
-      <c r="G9" t="s">
-        <v>396</v>
+      <c r="G9" s="4" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3619,13 +4049,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>187</v>
-      </c>
-      <c r="G10" t="s">
-        <v>397</v>
+        <v>185</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -3640,12 +4070,12 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3653,13 +4083,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="G4" t="s">
-        <v>381</v>
+      <c r="G4" s="4" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3667,13 +4097,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E5">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
-        <v>382</v>
+      <c r="G5" s="4" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3681,13 +4111,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E6">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
-        <v>383</v>
+      <c r="G6" s="4" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3695,13 +4125,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E7">
         <v>22</v>
       </c>
-      <c r="G7" t="s">
-        <v>388</v>
+      <c r="G7" s="4" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3709,13 +4139,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E8">
         <v>28</v>
       </c>
-      <c r="G8" t="s">
-        <v>390</v>
+      <c r="G8" s="4" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3723,13 +4153,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E9">
         <v>34</v>
       </c>
-      <c r="G9" t="s">
-        <v>384</v>
+      <c r="G9" s="4" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3737,13 +4167,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E10">
         <v>35</v>
       </c>
-      <c r="G10" t="s">
-        <v>385</v>
+      <c r="G10" s="4" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -3751,13 +4181,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E11">
         <v>43</v>
       </c>
-      <c r="G11" t="s">
-        <v>386</v>
+      <c r="G11" s="4" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -3765,13 +4195,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E12" t="s">
-        <v>191</v>
-      </c>
-      <c r="G12" t="s">
-        <v>387</v>
+        <v>189</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -3786,7 +4216,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -3794,10 +4224,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" t="s">
-        <v>376</v>
+        <v>118</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -3805,10 +4235,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" t="s">
-        <v>377</v>
+        <v>119</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -3816,10 +4246,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F5" t="s">
-        <v>378</v>
+        <v>120</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -3827,10 +4257,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" t="s">
-        <v>368</v>
+        <v>121</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -3838,10 +4268,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" t="s">
-        <v>379</v>
+        <v>122</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -3849,10 +4279,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F8" t="s">
-        <v>380</v>
+        <v>123</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -3860,10 +4290,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" t="s">
-        <v>369</v>
+        <v>124</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3871,10 +4301,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F10" t="s">
-        <v>370</v>
+        <v>125</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -3882,10 +4312,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" t="s">
-        <v>371</v>
+        <v>126</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -3893,10 +4323,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F12" t="s">
-        <v>372</v>
+        <v>127</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -3904,10 +4334,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F13" t="s">
-        <v>373</v>
+        <v>128</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3915,10 +4345,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
-      </c>
-      <c r="F14" t="s">
-        <v>374</v>
+        <v>129</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3926,10 +4356,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
-      </c>
-      <c r="F15" t="s">
-        <v>375</v>
+        <v>130</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3939,12 +4369,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -3952,13 +4382,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="I3" t="s">
-        <v>358</v>
+      <c r="I3" s="4" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -3966,13 +4396,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F4">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
-        <v>359</v>
+      <c r="I4" s="4" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3980,13 +4410,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F5">
         <v>44</v>
       </c>
-      <c r="I5" t="s">
-        <v>360</v>
+      <c r="I5" s="4" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -3994,13 +4424,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F6">
         <v>60</v>
       </c>
-      <c r="I6" t="s">
-        <v>361</v>
+      <c r="I6" s="4" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -4008,13 +4438,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F7">
         <v>76</v>
       </c>
-      <c r="I7" t="s">
-        <v>362</v>
+      <c r="I7" s="4" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -4022,13 +4452,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F8">
         <v>135</v>
       </c>
-      <c r="I8" t="s">
-        <v>363</v>
+      <c r="I8" s="4" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -4036,13 +4466,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F9">
         <v>160</v>
       </c>
-      <c r="I9" t="s">
-        <v>364</v>
+      <c r="I9" s="4" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -4050,13 +4480,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F10">
         <v>167</v>
       </c>
-      <c r="I10" t="s">
-        <v>365</v>
+      <c r="I10" s="4" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -4064,13 +4494,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F11">
         <v>170</v>
       </c>
-      <c r="I11" t="s">
-        <v>367</v>
+      <c r="I11" s="4" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -4078,13 +4508,18 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F12" t="s">
-        <v>198</v>
-      </c>
-      <c r="I12" t="s">
-        <v>366</v>
+        <v>196</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I13" s="4" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -4099,12 +4534,12 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -4112,13 +4547,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
-      <c r="I3" t="s">
-        <v>351</v>
+      <c r="I3" s="4" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4126,13 +4561,13 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G4">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
-        <v>340</v>
+      <c r="I4" s="4" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -4140,13 +4575,13 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G5">
         <v>10</v>
       </c>
-      <c r="I5" t="s">
-        <v>341</v>
+      <c r="I5" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -4154,13 +4589,13 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G6">
         <v>11</v>
       </c>
-      <c r="I6" t="s">
-        <v>342</v>
+      <c r="I6" s="4" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -4168,13 +4603,13 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G7">
         <v>12</v>
       </c>
-      <c r="I7" t="s">
-        <v>352</v>
+      <c r="I7" s="4" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -4182,13 +4617,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G8">
         <v>13</v>
       </c>
-      <c r="I8" t="s">
-        <v>353</v>
+      <c r="I8" s="4" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -4196,13 +4631,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G9">
         <v>14</v>
       </c>
-      <c r="I9" t="s">
-        <v>389</v>
+      <c r="I9" s="4" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -4210,13 +4645,13 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G10">
         <v>16</v>
       </c>
-      <c r="I10" t="s">
-        <v>343</v>
+      <c r="I10" s="4" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -4224,13 +4659,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G11">
         <v>18</v>
       </c>
-      <c r="I11" t="s">
-        <v>344</v>
+      <c r="I11" s="4" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -4238,13 +4673,13 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G12">
         <v>22</v>
       </c>
-      <c r="I12" t="s">
-        <v>345</v>
+      <c r="I12" s="4" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -4252,13 +4687,13 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G13">
         <v>23</v>
       </c>
-      <c r="I13" t="s">
-        <v>346</v>
+      <c r="I13" s="4" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -4266,13 +4701,13 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G14">
         <v>24</v>
       </c>
-      <c r="I14" t="s">
-        <v>354</v>
+      <c r="I14" s="4" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -4280,13 +4715,13 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G15">
         <v>25</v>
       </c>
-      <c r="I15" t="s">
-        <v>347</v>
+      <c r="I15" s="4" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -4294,13 +4729,13 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G16">
         <v>26</v>
       </c>
-      <c r="I16" t="s">
-        <v>355</v>
+      <c r="I16" s="4" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
@@ -4308,13 +4743,13 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G17">
         <v>28</v>
       </c>
-      <c r="I17" t="s">
-        <v>356</v>
+      <c r="I17" s="4" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
@@ -4322,13 +4757,13 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G18">
         <v>29</v>
       </c>
-      <c r="I18" t="s">
-        <v>348</v>
+      <c r="I18" s="4" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
@@ -4336,13 +4771,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G19">
         <v>32</v>
       </c>
-      <c r="I19" t="s">
-        <v>349</v>
+      <c r="I19" s="4" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
@@ -4350,13 +4785,13 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G20">
         <v>33</v>
       </c>
-      <c r="I20" t="s">
-        <v>350</v>
+      <c r="I20" s="4" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
@@ -4364,18 +4799,18 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G21">
         <v>34</v>
       </c>
-      <c r="I21" t="s">
-        <v>357</v>
+      <c r="I21" s="4" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G22" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
+++ b/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667" activeTab="13"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="CetaForm" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,6 @@
     <sheet name="Altec" sheetId="10" r:id="rId11"/>
     <sheet name="Stubai" sheetId="11" r:id="rId12"/>
     <sheet name="HFS" sheetId="12" r:id="rId13"/>
-    <sheet name="Insize (2)" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="453">
   <si>
     <t>TOOL CONTAINERS AND ASSORTMENTS</t>
   </si>
@@ -1348,15 +1347,9 @@
     <t>Рачни и машински либели</t>
   </si>
   <si>
-    <t>Линеари, дигитални индикатори, воздушни мерила, тестери за истекување на воздух, ласерски скен микрометри, спектрометри, преднаместувачи на алати</t>
-  </si>
-  <si>
     <t>Разновидни детектори</t>
   </si>
   <si>
-    <t>(cmm) координатни мерни машини</t>
-  </si>
-  <si>
     <t>Профил проектори, системи за брзо мерење, визуелни мерни системи</t>
   </si>
   <si>
@@ -1399,64 +1392,10 @@
     <t>Мерач на спреј на сол, комори за температура и влажност</t>
   </si>
   <si>
-    <t>Insize 1. Експорт на податоци и софтвер</t>
-  </si>
-  <si>
-    <t>Insize 10. Мерачи на косини</t>
-  </si>
-  <si>
-    <t>Insize 2. Шублери</t>
-  </si>
-  <si>
-    <t>Insize 3. Мерачи на длабочина</t>
-  </si>
-  <si>
-    <t>Insize 4. Мерачи на висина</t>
-  </si>
-  <si>
-    <t>Insize 5. Компаратори</t>
-  </si>
-  <si>
-    <t>Insize 6. Микрометри</t>
-  </si>
-  <si>
-    <t>Insize 7. Мерачи на дијаметар и опсег на отвори</t>
-  </si>
-  <si>
-    <t>Insize 8. Мерачи на радиус на лак</t>
-  </si>
-  <si>
-    <t>Insize 9. Мерачи на жлебови за клучеви</t>
-  </si>
-  <si>
-    <t>Insize 1. DATA OUTPUT AND SOFTWARE.pdf</t>
-  </si>
-  <si>
-    <t>Insize 2. CALIPERS.pdf</t>
-  </si>
-  <si>
-    <t>Insize 3. DEPTH MEASUREMENT.pdf</t>
-  </si>
-  <si>
-    <t>Insize 4. HEIGHT MEASUREMENT.pdf</t>
-  </si>
-  <si>
-    <t>Insize 5. COMPARISON INSTRUMENTS.pdf</t>
-  </si>
-  <si>
-    <t>Insize 6. MICROMETERS.pdf</t>
-  </si>
-  <si>
-    <t>Insize 7. BORE DIAMETER, CIRCUMFERENCE MEASUREMENT.pdf</t>
-  </si>
-  <si>
-    <t>Insize 8. ARC RADIUS MEASUREMENT.pdf</t>
-  </si>
-  <si>
-    <t>Insize 9. KEYWAY MEASUREMENT.pdf</t>
-  </si>
-  <si>
-    <t>Insize 10. CHAMFER MEASUREMENT.pdf</t>
+    <t>Линеари, дигитални индикатори, воздушни мерила, тестери за истекување на воздух, ласерски скен микрометри, спектрометри</t>
+  </si>
+  <si>
+    <t>CMM - координатни мерни машини</t>
   </si>
 </sst>
 </file>
@@ -2945,137 +2884,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>463</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="C2" t="str">
-        <f>"Rename-Item -LiteralPath '"&amp;A2&amp;"' -NewName """&amp;SUBSTITUTE(B2,"""","`"") &amp; """"")</f>
-        <v>Rename-Item -LiteralPath 'Insize 1. DATA OUTPUT AND SOFTWARE.pdf' -NewName "Insize 1. Експорт на податоци и софтвер</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>464</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="C3" t="str">
-        <f t="shared" ref="C3:C11" si="0">"Rename-Item -LiteralPath '"&amp;A3&amp;"' -NewName """&amp;SUBSTITUTE(B3,"""","`"") &amp; """"")</f>
-        <v>Rename-Item -LiteralPath 'Insize 2. CALIPERS.pdf' -NewName "Insize 2. Шублери</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>465</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rename-Item -LiteralPath 'Insize 3. DEPTH MEASUREMENT.pdf' -NewName "Insize 3. Мерачи на длабочина</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>466</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="C5" t="str">
-        <f t="shared" si="0"/>
-        <v>Rename-Item -LiteralPath 'Insize 4. HEIGHT MEASUREMENT.pdf' -NewName "Insize 4. Мерачи на висина</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>467</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="C6" t="str">
-        <f t="shared" si="0"/>
-        <v>Rename-Item -LiteralPath 'Insize 5. COMPARISON INSTRUMENTS.pdf' -NewName "Insize 5. Компаратори</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>468</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="C7" t="str">
-        <f t="shared" si="0"/>
-        <v>Rename-Item -LiteralPath 'Insize 6. MICROMETERS.pdf' -NewName "Insize 6. Микрометри</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>469</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C8" t="str">
-        <f t="shared" si="0"/>
-        <v>Rename-Item -LiteralPath 'Insize 7. BORE DIAMETER, CIRCUMFERENCE MEASUREMENT.pdf' -NewName "Insize 7. Мерачи на дијаметар и опсег на отвори</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>470</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="C9" t="str">
-        <f t="shared" si="0"/>
-        <v>Rename-Item -LiteralPath 'Insize 8. ARC RADIUS MEASUREMENT.pdf' -NewName "Insize 8. Мерачи на радиус на лак</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>471</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="C10" t="str">
-        <f t="shared" si="0"/>
-        <v>Rename-Item -LiteralPath 'Insize 9. KEYWAY MEASUREMENT.pdf' -NewName "Insize 9. Мерачи на жлебови за клучеви</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>472</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="C11" t="str">
-        <f t="shared" si="0"/>
-        <v>Rename-Item -LiteralPath 'Insize 10. CHAMFER MEASUREMENT.pdf' -NewName "Insize 10. Мерачи на косини</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q21"/>
@@ -3510,419 +3318,419 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>82</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>83</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>84</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>85</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>86</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>87</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>88</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>89</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>90</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>91</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>92</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>93</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>75</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>76</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>94</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>80</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>183</v>
       </c>
-      <c r="O23" s="4" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G23" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>95</v>
       </c>
-      <c r="O24" s="4" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G24" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>96</v>
       </c>
-      <c r="O25" s="4" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G25" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
       </c>
-      <c r="O26" s="4" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G26" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>98</v>
       </c>
-      <c r="O27" s="4" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G27" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>99</v>
       </c>
-      <c r="O28" s="4" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G28" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>100</v>
       </c>
-      <c r="O29" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G29" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>79</v>
       </c>
-      <c r="O30" s="4" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G30" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>101</v>
       </c>
-      <c r="O31" s="4" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G31" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
         <v>102</v>
       </c>
-      <c r="O32" s="4" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G32" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>78</v>
       </c>
-      <c r="O33" s="4" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G33" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>81</v>
       </c>
-      <c r="O34" s="4" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G34" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>103</v>
       </c>
-      <c r="O35" s="4" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G35" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>104</v>
       </c>
-      <c r="O36" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G36" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>105</v>
       </c>
-      <c r="O37" s="4" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G37" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>77</v>
       </c>
-      <c r="O38" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="G38" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
         <v>106</v>
       </c>
-      <c r="O39" s="4" t="s">
-        <v>452</v>
+      <c r="G39" s="4" t="s">
+        <v>450</v>
       </c>
     </row>
   </sheetData>

--- a/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
+++ b/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667" firstSheet="6" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="CetaForm" sheetId="1" r:id="rId1"/>
@@ -984,9 +984,6 @@
     <t>Еднорачни стеги</t>
   </si>
   <si>
-    <t>Пружински стеги</t>
-  </si>
-  <si>
     <t>Стеги со ремен</t>
   </si>
   <si>
@@ -1116,9 +1113,6 @@
     <t>Клешти и секачи</t>
   </si>
   <si>
-    <t>Изолиран 1000 V алат и мултимери</t>
-  </si>
-  <si>
     <t>Штрафцигери и клешти за електроника</t>
   </si>
   <si>
@@ -1167,9 +1161,6 @@
     <t>Дијамантски пили</t>
   </si>
   <si>
-    <t>Дијамантски круни за бушење</t>
-  </si>
-  <si>
     <t>Дијамантски алат за брусење</t>
   </si>
   <si>
@@ -1275,18 +1266,12 @@
     <t>Вакум рачки</t>
   </si>
   <si>
-    <t>Платформа за пилирање</t>
-  </si>
-  <si>
     <t>AluLight Професионално подвижно скеле со скали</t>
   </si>
   <si>
     <t>AluSteg - мостови за скелиња</t>
   </si>
   <si>
-    <t>АЛАТ ЗА ПОПРАВКА НА НАВОЈ</t>
-  </si>
-  <si>
     <t>Експорт на податоци и софтвер</t>
   </si>
   <si>
@@ -1396,6 +1381,21 @@
   </si>
   <si>
     <t>CMM - координатни мерни машини</t>
+  </si>
+  <si>
+    <t>VDE Изолиран 1000 V алат и мултимери</t>
+  </si>
+  <si>
+    <t>Дијамантски прстени за сечење</t>
+  </si>
+  <si>
+    <t>Алат за поправка на навој</t>
+  </si>
+  <si>
+    <t>Стеги со пружини</t>
+  </si>
+  <si>
+    <t>Платформи за пилирање</t>
   </si>
 </sst>
 </file>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2031,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2042,7 +2042,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2053,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2064,7 +2064,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2075,7 +2075,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2086,7 +2086,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>359</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2097,7 +2097,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2108,7 +2108,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2119,7 +2119,7 @@
         <v>18</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2130,7 +2130,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2141,7 +2141,7 @@
         <v>22</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2152,7 +2152,7 @@
         <v>24</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2163,7 +2163,7 @@
         <v>26</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -2195,8 +2195,11 @@
       <c r="D3" t="s">
         <v>200</v>
       </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="J3" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2209,6 +2212,9 @@
       <c r="D4" t="s">
         <v>202</v>
       </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
       <c r="J4" s="4" t="s">
         <v>308</v>
       </c>
@@ -2223,8 +2229,11 @@
       <c r="D5" t="s">
         <v>203</v>
       </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
       <c r="J5" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2237,6 +2246,9 @@
       <c r="D6" t="s">
         <v>205</v>
       </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
       <c r="J6" s="4" t="s">
         <v>309</v>
       </c>
@@ -2251,6 +2263,9 @@
       <c r="D7" t="s">
         <v>207</v>
       </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
       <c r="J7" s="4" t="s">
         <v>310</v>
       </c>
@@ -2265,6 +2280,9 @@
       <c r="D8" t="s">
         <v>208</v>
       </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
       <c r="J8" s="4" t="s">
         <v>311</v>
       </c>
@@ -2279,6 +2297,9 @@
       <c r="D9" t="s">
         <v>210</v>
       </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
       <c r="J9" s="4" t="s">
         <v>312</v>
       </c>
@@ -2293,6 +2314,9 @@
       <c r="D10" t="s">
         <v>212</v>
       </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
       <c r="J10" s="4" t="s">
         <v>313</v>
       </c>
@@ -2307,6 +2331,9 @@
       <c r="D11" t="s">
         <v>214</v>
       </c>
+      <c r="I11">
+        <v>9</v>
+      </c>
       <c r="J11" s="4" t="s">
         <v>314</v>
       </c>
@@ -2321,8 +2348,11 @@
       <c r="D12" t="s">
         <v>216</v>
       </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
       <c r="J12" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -2335,8 +2365,11 @@
       <c r="D13" t="s">
         <v>218</v>
       </c>
+      <c r="I13">
+        <v>11</v>
+      </c>
       <c r="J13" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2349,8 +2382,11 @@
       <c r="D14" t="s">
         <v>220</v>
       </c>
+      <c r="I14">
+        <v>12</v>
+      </c>
       <c r="J14" s="4" t="s">
-        <v>315</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2363,8 +2399,11 @@
       <c r="D15" t="s">
         <v>222</v>
       </c>
+      <c r="I15">
+        <v>13</v>
+      </c>
       <c r="J15" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -2377,8 +2416,11 @@
       <c r="D16" t="s">
         <v>224</v>
       </c>
+      <c r="I16">
+        <v>14</v>
+      </c>
       <c r="J16" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -2391,8 +2433,11 @@
       <c r="D17" t="s">
         <v>226</v>
       </c>
+      <c r="I17">
+        <v>15</v>
+      </c>
       <c r="J17" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
@@ -2405,8 +2450,11 @@
       <c r="D18" t="s">
         <v>228</v>
       </c>
+      <c r="I18">
+        <v>16</v>
+      </c>
       <c r="J18" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
@@ -2419,8 +2467,11 @@
       <c r="D19" t="s">
         <v>230</v>
       </c>
+      <c r="I19">
+        <v>17</v>
+      </c>
       <c r="J19" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
@@ -2433,8 +2484,11 @@
       <c r="D20" t="s">
         <v>232</v>
       </c>
+      <c r="I20">
+        <v>18</v>
+      </c>
       <c r="J20" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
@@ -2447,8 +2501,11 @@
       <c r="D21" t="s">
         <v>234</v>
       </c>
+      <c r="I21">
+        <v>19</v>
+      </c>
       <c r="J21" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
@@ -2461,8 +2518,11 @@
       <c r="D22" t="s">
         <v>237</v>
       </c>
+      <c r="I22">
+        <v>20</v>
+      </c>
       <c r="J22" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
@@ -2475,8 +2535,11 @@
       <c r="D23" t="s">
         <v>239</v>
       </c>
+      <c r="I23">
+        <v>21</v>
+      </c>
       <c r="J23" s="4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
@@ -2489,8 +2552,11 @@
       <c r="D24" t="s">
         <v>241</v>
       </c>
+      <c r="I24">
+        <v>22</v>
+      </c>
       <c r="J24" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
@@ -2503,8 +2569,11 @@
       <c r="D25" t="s">
         <v>243</v>
       </c>
+      <c r="I25">
+        <v>23</v>
+      </c>
       <c r="J25" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
@@ -2517,8 +2586,11 @@
       <c r="D26" t="s">
         <v>245</v>
       </c>
+      <c r="I26">
+        <v>24</v>
+      </c>
       <c r="J26" s="4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
@@ -2531,8 +2603,11 @@
       <c r="D27" t="s">
         <v>247</v>
       </c>
+      <c r="I27">
+        <v>25</v>
+      </c>
       <c r="J27" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
@@ -2545,8 +2620,11 @@
       <c r="D28" t="s">
         <v>249</v>
       </c>
+      <c r="I28">
+        <v>26</v>
+      </c>
       <c r="J28" s="4" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
@@ -2559,8 +2637,11 @@
       <c r="D29" t="s">
         <v>251</v>
       </c>
+      <c r="I29">
+        <v>27</v>
+      </c>
       <c r="J29" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
@@ -2573,8 +2654,11 @@
       <c r="D30" t="s">
         <v>253</v>
       </c>
+      <c r="I30">
+        <v>28</v>
+      </c>
       <c r="J30" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
@@ -2587,8 +2671,11 @@
       <c r="D31" t="s">
         <v>255</v>
       </c>
+      <c r="I31">
+        <v>29</v>
+      </c>
       <c r="J31" s="4" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
@@ -2601,8 +2688,11 @@
       <c r="D32" t="s">
         <v>258</v>
       </c>
+      <c r="I32">
+        <v>30</v>
+      </c>
       <c r="J32" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -2633,6 +2723,9 @@
       <c r="D2" t="s">
         <v>260</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2" s="4" t="s">
         <v>294</v>
       </c>
@@ -2647,6 +2740,9 @@
       <c r="D3" t="s">
         <v>261</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3" s="4" t="s">
         <v>295</v>
       </c>
@@ -2661,6 +2757,9 @@
       <c r="D4" t="s">
         <v>262</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
       <c r="J4" s="4" t="s">
         <v>296</v>
       </c>
@@ -2675,6 +2774,9 @@
       <c r="D5" t="s">
         <v>284</v>
       </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
       <c r="J5" s="4" t="s">
         <v>297</v>
       </c>
@@ -2689,6 +2791,9 @@
       <c r="D6" t="s">
         <v>285</v>
       </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
       <c r="J6" s="4" t="s">
         <v>298</v>
       </c>
@@ -2703,6 +2808,9 @@
       <c r="D7" t="s">
         <v>263</v>
       </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
       <c r="J7" s="4" t="s">
         <v>299</v>
       </c>
@@ -2717,6 +2825,9 @@
       <c r="D8" t="s">
         <v>286</v>
       </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
       <c r="J8" s="4" t="s">
         <v>300</v>
       </c>
@@ -2731,6 +2842,9 @@
       <c r="D9" t="s">
         <v>287</v>
       </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
       <c r="J9" s="4" t="s">
         <v>301</v>
       </c>
@@ -2745,6 +2859,9 @@
       <c r="D10" t="s">
         <v>288</v>
       </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
       <c r="J10" s="4" t="s">
         <v>288</v>
       </c>
@@ -2759,6 +2876,9 @@
       <c r="D11" t="s">
         <v>289</v>
       </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
       <c r="J11" s="4" t="s">
         <v>307</v>
       </c>
@@ -2773,6 +2893,9 @@
       <c r="D12" t="s">
         <v>264</v>
       </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
       <c r="J12" s="4" t="s">
         <v>302</v>
       </c>
@@ -2787,6 +2910,9 @@
       <c r="D13" t="s">
         <v>290</v>
       </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
       <c r="J13" s="4" t="s">
         <v>303</v>
       </c>
@@ -2801,6 +2927,9 @@
       <c r="D14" t="s">
         <v>291</v>
       </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
       <c r="J14" s="4" t="s">
         <v>304</v>
       </c>
@@ -2815,6 +2944,9 @@
       <c r="D15" t="s">
         <v>292</v>
       </c>
+      <c r="I15">
+        <v>14</v>
+      </c>
       <c r="J15" s="4" t="s">
         <v>305</v>
       </c>
@@ -2829,8 +2961,11 @@
       <c r="D16" t="s">
         <v>293</v>
       </c>
+      <c r="I16">
+        <v>15</v>
+      </c>
       <c r="J16" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -2843,6 +2978,9 @@
       <c r="D17" t="s">
         <v>265</v>
       </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
       <c r="J17" s="4" t="s">
         <v>306</v>
       </c>
@@ -2857,8 +2995,11 @@
       <c r="D18" t="s">
         <v>266</v>
       </c>
+      <c r="I18">
+        <v>17</v>
+      </c>
       <c r="J18" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -2928,7 +3069,7 @@
         <v>55</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="Q5" t="s">
         <v>30</v>
@@ -3081,7 +3222,7 @@
         <v>33</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Q14" t="s">
         <v>44</v>
@@ -3334,7 +3475,7 @@
         <v>82</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3345,7 +3486,7 @@
         <v>71</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3356,7 +3497,7 @@
         <v>83</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3367,7 +3508,7 @@
         <v>84</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3378,7 +3519,7 @@
         <v>85</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3389,7 +3530,7 @@
         <v>72</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3400,7 +3541,7 @@
         <v>86</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3411,7 +3552,7 @@
         <v>87</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -3422,7 +3563,7 @@
         <v>88</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -3433,7 +3574,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -3444,7 +3585,7 @@
         <v>90</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -3455,7 +3596,7 @@
         <v>73</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -3466,7 +3607,7 @@
         <v>91</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -3477,7 +3618,7 @@
         <v>74</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -3488,7 +3629,7 @@
         <v>92</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -3499,7 +3640,7 @@
         <v>93</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -3510,7 +3651,7 @@
         <v>75</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -3521,7 +3662,7 @@
         <v>76</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -3532,7 +3673,7 @@
         <v>94</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -3543,7 +3684,7 @@
         <v>80</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -3554,7 +3695,7 @@
         <v>183</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -3565,7 +3706,7 @@
         <v>95</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -3576,7 +3717,7 @@
         <v>96</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -3587,7 +3728,7 @@
         <v>97</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -3598,7 +3739,7 @@
         <v>98</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -3609,7 +3750,7 @@
         <v>99</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -3620,7 +3761,7 @@
         <v>100</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -3631,7 +3772,7 @@
         <v>79</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -3642,7 +3783,7 @@
         <v>101</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -3653,7 +3794,7 @@
         <v>102</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -3664,7 +3805,7 @@
         <v>78</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -3675,7 +3816,7 @@
         <v>81</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -3686,7 +3827,7 @@
         <v>103</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -3697,7 +3838,7 @@
         <v>104</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -3708,7 +3849,7 @@
         <v>105</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -3719,7 +3860,7 @@
         <v>77</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -3730,7 +3871,7 @@
         <v>106</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -3765,7 +3906,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3779,7 +3920,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3793,7 +3934,7 @@
         <v>23</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3807,7 +3948,7 @@
         <v>37</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3821,7 +3962,7 @@
         <v>59</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3835,7 +3976,7 @@
         <v>66</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3849,7 +3990,7 @@
         <v>69</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3863,7 +4004,7 @@
         <v>185</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3897,7 +4038,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3911,7 +4052,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3925,7 +4066,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>376</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3939,7 +4080,7 @@
         <v>22</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3953,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3967,7 +4108,7 @@
         <v>34</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3981,7 +4122,7 @@
         <v>35</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -3995,7 +4136,7 @@
         <v>43</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -4009,7 +4150,7 @@
         <v>189</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -4035,7 +4176,7 @@
         <v>118</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -4046,7 +4187,7 @@
         <v>119</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -4057,7 +4198,7 @@
         <v>120</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -4068,7 +4209,7 @@
         <v>121</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -4079,7 +4220,7 @@
         <v>122</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -4090,7 +4231,7 @@
         <v>123</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -4101,7 +4242,7 @@
         <v>124</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -4112,7 +4253,7 @@
         <v>125</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -4123,7 +4264,7 @@
         <v>126</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -4134,7 +4275,7 @@
         <v>127</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -4145,7 +4286,7 @@
         <v>128</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -4156,7 +4297,7 @@
         <v>129</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -4167,7 +4308,7 @@
         <v>130</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -4195,8 +4336,11 @@
       <c r="F3">
         <v>8</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
       <c r="I3" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4209,8 +4353,11 @@
       <c r="F4">
         <v>14</v>
       </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
       <c r="I4" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -4223,8 +4370,11 @@
       <c r="F5">
         <v>44</v>
       </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
       <c r="I5" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -4237,8 +4387,11 @@
       <c r="F6">
         <v>60</v>
       </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
       <c r="I6" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -4251,8 +4404,11 @@
       <c r="F7">
         <v>76</v>
       </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
       <c r="I7" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -4265,8 +4421,11 @@
       <c r="F8">
         <v>135</v>
       </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
       <c r="I8" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -4279,8 +4438,11 @@
       <c r="F9">
         <v>160</v>
       </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
       <c r="I9" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -4293,8 +4455,11 @@
       <c r="F10">
         <v>167</v>
       </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
       <c r="I10" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -4307,8 +4472,11 @@
       <c r="F11">
         <v>170</v>
       </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
       <c r="I11" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -4321,13 +4489,19 @@
       <c r="F12" t="s">
         <v>196</v>
       </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
       <c r="I12" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>11</v>
+      </c>
       <c r="I13" s="4" t="s">
-        <v>415</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -4337,287 +4511,287 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s">
         <v>144</v>
       </c>
-      <c r="G3">
+      <c r="F3">
         <v>4</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8">
+        <v>13</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9">
+        <v>14</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11">
+        <v>18</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>147</v>
-      </c>
-      <c r="G6">
+      <c r="B12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12">
+        <v>22</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7">
+      <c r="B13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13">
+        <v>23</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>149</v>
-      </c>
-      <c r="G8">
+      <c r="B14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14">
+        <v>24</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>13</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="B15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15">
+        <v>25</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16">
+        <v>26</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G9">
-        <v>14</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>151</v>
-      </c>
-      <c r="G10">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17">
+        <v>28</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>16</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>152</v>
-      </c>
-      <c r="G11">
+      <c r="B18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18">
+        <v>29</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19">
+        <v>32</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>18</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G12">
-        <v>22</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>154</v>
-      </c>
-      <c r="G13">
-        <v>23</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>155</v>
-      </c>
-      <c r="G14">
-        <v>24</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>156</v>
-      </c>
-      <c r="G15">
-        <v>25</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>157</v>
-      </c>
-      <c r="G16">
-        <v>26</v>
-      </c>
-      <c r="I16" s="4" t="s">
+      <c r="B20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20">
+        <v>33</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F21">
+        <v>34</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G17">
-        <v>28</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>159</v>
-      </c>
-      <c r="G18">
-        <v>29</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>160</v>
-      </c>
-      <c r="G19">
-        <v>32</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20">
-        <v>18</v>
-      </c>
-      <c r="C20" t="s">
-        <v>161</v>
-      </c>
-      <c r="G20">
-        <v>33</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21">
-        <v>19</v>
-      </c>
-      <c r="C21" t="s">
-        <v>162</v>
-      </c>
-      <c r="G21">
-        <v>34</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G22" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
         <v>197</v>
       </c>
     </row>

--- a/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
+++ b/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667" firstSheet="6" activeTab="10"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667"/>
   </bookViews>
   <sheets>
     <sheet name="CetaForm" sheetId="1" r:id="rId1"/>
@@ -1020,9 +1020,6 @@
     <t>Батериски производи</t>
   </si>
   <si>
-    <t>Rodflex-алатки</t>
-  </si>
-  <si>
     <t>Мини алати</t>
   </si>
   <si>
@@ -1396,6 +1393,9 @@
   </si>
   <si>
     <t>Платформи за пилирање</t>
+  </si>
+  <si>
+    <t>Rodflex-алати</t>
   </si>
 </sst>
 </file>
@@ -1574,8 +1574,8 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>184180</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2003,6 +2003,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="6" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2020,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2031,7 +2034,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -2042,7 +2045,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -2053,7 +2056,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -2064,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2075,7 +2078,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2086,7 +2089,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -2097,7 +2100,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2108,7 +2111,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2119,7 +2122,7 @@
         <v>18</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -2130,7 +2133,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2141,7 +2144,7 @@
         <v>22</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2152,7 +2155,7 @@
         <v>24</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2163,7 +2166,7 @@
         <v>26</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -2199,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2233,7 +2236,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2352,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -2369,7 +2372,7 @@
         <v>11</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2386,7 +2389,7 @@
         <v>12</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2403,7 +2406,7 @@
         <v>13</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -2420,7 +2423,7 @@
         <v>14</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -2505,7 +2508,7 @@
         <v>19</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
@@ -2522,7 +2525,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
@@ -2539,7 +2542,7 @@
         <v>21</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
@@ -2573,7 +2576,7 @@
         <v>23</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
@@ -2590,7 +2593,7 @@
         <v>24</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
@@ -2607,7 +2610,7 @@
         <v>25</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
@@ -2624,7 +2627,7 @@
         <v>26</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
@@ -2641,7 +2644,7 @@
         <v>27</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
@@ -2675,7 +2678,7 @@
         <v>29</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
@@ -2965,7 +2968,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -2999,7 +3002,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -3029,6 +3032,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="13" max="13" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -3069,7 +3075,7 @@
         <v>55</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q5" t="s">
         <v>30</v>
@@ -3222,7 +3228,7 @@
         <v>33</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q14" t="s">
         <v>44</v>
@@ -3475,7 +3481,7 @@
         <v>82</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3486,7 +3492,7 @@
         <v>71</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3497,7 +3503,7 @@
         <v>83</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3508,7 +3514,7 @@
         <v>84</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3519,7 +3525,7 @@
         <v>85</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3530,7 +3536,7 @@
         <v>72</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3541,7 +3547,7 @@
         <v>86</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3552,7 +3558,7 @@
         <v>87</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -3563,7 +3569,7 @@
         <v>88</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -3574,7 +3580,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -3585,7 +3591,7 @@
         <v>90</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -3596,7 +3602,7 @@
         <v>73</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -3607,7 +3613,7 @@
         <v>91</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -3618,7 +3624,7 @@
         <v>74</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -3629,7 +3635,7 @@
         <v>92</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -3640,7 +3646,7 @@
         <v>93</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -3651,7 +3657,7 @@
         <v>75</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -3662,7 +3668,7 @@
         <v>76</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -3673,7 +3679,7 @@
         <v>94</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -3684,7 +3690,7 @@
         <v>80</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -3695,7 +3701,7 @@
         <v>183</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -3706,7 +3712,7 @@
         <v>95</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -3717,7 +3723,7 @@
         <v>96</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -3728,7 +3734,7 @@
         <v>97</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -3739,7 +3745,7 @@
         <v>98</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -3750,7 +3756,7 @@
         <v>99</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -3761,7 +3767,7 @@
         <v>100</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -3772,7 +3778,7 @@
         <v>79</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -3783,7 +3789,7 @@
         <v>101</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -3794,7 +3800,7 @@
         <v>102</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -3805,7 +3811,7 @@
         <v>78</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -3816,7 +3822,7 @@
         <v>81</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -3827,7 +3833,7 @@
         <v>103</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -3838,7 +3844,7 @@
         <v>104</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -3849,7 +3855,7 @@
         <v>105</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -3860,7 +3866,7 @@
         <v>77</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -3871,7 +3877,7 @@
         <v>106</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -3884,6 +3890,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="6" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3906,7 +3915,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3920,7 +3929,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3934,7 +3943,7 @@
         <v>23</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3948,7 +3957,7 @@
         <v>37</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3962,7 +3971,7 @@
         <v>59</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3976,7 +3985,7 @@
         <v>66</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3990,7 +3999,7 @@
         <v>69</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -4004,7 +4013,7 @@
         <v>185</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -4016,6 +4025,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="6" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -4038,7 +4050,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -4052,7 +4064,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4066,7 +4078,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4080,7 +4092,7 @@
         <v>22</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -4094,7 +4106,7 @@
         <v>28</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -4108,7 +4120,7 @@
         <v>34</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -4122,7 +4134,7 @@
         <v>35</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -4136,7 +4148,7 @@
         <v>43</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -4150,7 +4162,7 @@
         <v>189</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -4162,6 +4174,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="5" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -4176,7 +4191,7 @@
         <v>118</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -4187,7 +4202,7 @@
         <v>119</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -4198,7 +4213,7 @@
         <v>120</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -4209,7 +4224,7 @@
         <v>121</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -4220,7 +4235,7 @@
         <v>122</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -4231,7 +4246,7 @@
         <v>123</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -4242,7 +4257,7 @@
         <v>124</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -4253,7 +4268,7 @@
         <v>125</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -4264,7 +4279,7 @@
         <v>126</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -4275,7 +4290,7 @@
         <v>127</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -4286,7 +4301,7 @@
         <v>128</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -4297,7 +4312,7 @@
         <v>129</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -4308,7 +4323,7 @@
         <v>130</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -4340,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4357,7 +4372,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -4374,7 +4389,7 @@
         <v>3</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -4391,7 +4406,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -4408,7 +4423,7 @@
         <v>5</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -4425,7 +4440,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -4442,7 +4457,7 @@
         <v>7</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -4459,7 +4474,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -4476,7 +4491,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -4493,7 +4508,7 @@
         <v>10</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -4501,7 +4516,7 @@
         <v>11</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -4513,6 +4528,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="7" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -4549,7 +4567,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -4563,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -4577,7 +4595,7 @@
         <v>11</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -4591,7 +4609,7 @@
         <v>12</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>327</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -4605,7 +4623,7 @@
         <v>13</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -4619,7 +4637,7 @@
         <v>14</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -4633,7 +4651,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -4647,7 +4665,7 @@
         <v>18</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -4675,7 +4693,7 @@
         <v>23</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -4689,7 +4707,7 @@
         <v>24</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -4703,7 +4721,7 @@
         <v>25</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -4717,7 +4735,7 @@
         <v>26</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -4731,7 +4749,7 @@
         <v>28</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -4787,7 +4805,7 @@
         <v>34</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">

--- a/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
+++ b/Javascript Vanilla/tehnohaus.mk/katalozi/Kategorii od katalozi.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="667" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="CetaForm" sheetId="1" r:id="rId1"/>
